--- a/templates/装箱单发票的格式.xlsx
+++ b/templates/装箱单发票的格式.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44E7A263-A04C-4B6F-934E-CCC894CACDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC15DD23-0E8E-484A-B187-E07C1CCDC819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="108" windowWidth="15324" windowHeight="15744"/>
+    <workbookView xWindow="2136" yWindow="480" windowWidth="15324" windowHeight="15744" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOICE" sheetId="1" r:id="rId1"/>
@@ -73,6 +73,7 @@
         <vertAlign val="subscript"/>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>……………………………………</t>
@@ -135,6 +136,7 @@
         <b/>
         <sz val="22"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -144,6 +146,7 @@
         <b/>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（重量单）</t>
@@ -198,10 +201,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>FEB.04.2026</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>YWSJ2602044</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -828,18 +827,22 @@
       </rPr>
       <t>22}</t>
     </r>
+  </si>
+  <si>
+    <t>{发票日期}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="[$USD]\ #,##0.00;[$USD]\ \-#,##0.00"/>
     <numFmt numFmtId="178" formatCode="[$USD]\ #,##0.00_);[Red]\([$USD]\ #,##0.00\)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -849,17 +852,20 @@
       <b/>
       <sz val="24"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -871,12 +877,14 @@
       <b/>
       <sz val="26"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -913,16 +921,19 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="20"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="24"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -939,62 +950,68 @@
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1002,6 +1019,7 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1009,12 +1027,6 @@
       <color rgb="FF2E3033"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1191,7 +1203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1258,7 +1270,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1267,7 +1279,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1366,6 +1378,9 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1373,6 +1388,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1402,27 +1438,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1438,13 +1453,10 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1452,14 +1464,11 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1760,7 +1769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:O43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
@@ -1776,53 +1785,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="65" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="66"/>
+      <c r="G4" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="74"/>
       <c r="I4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
-      <c r="E5" s="73"/>
+      <c r="E5" s="65"/>
       <c r="F5" s="27" t="s">
         <v>5</v>
       </c>
@@ -1834,22 +1843,22 @@
       <c r="K5" s="53"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1">
-      <c r="E6" s="74" t="s">
+      <c r="E6" s="66" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="66"/>
+      <c r="G6" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="74"/>
       <c r="I6" s="3"/>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1">
       <c r="A7" s="28"/>
-      <c r="E7" s="74"/>
+      <c r="E7" s="66"/>
       <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
@@ -1889,20 +1898,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="63" t="s">
+      <c r="D10" s="75"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="69"/>
-      <c r="H10" s="61" t="s">
+      <c r="G10" s="77"/>
+      <c r="H10" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="63"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="34" t="s">
@@ -1912,10 +1921,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="76"/>
+      <c r="G11" s="68"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="J11" s="50"/>
@@ -1929,8 +1938,8 @@
       <c r="D12" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="87" t="s">
-        <v>46</v>
+      <c r="E12" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="F12" s="38">
         <v>11</v>
@@ -1938,12 +1947,12 @@
       <c r="G12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="58">
+      <c r="H12" s="59">
         <f>F12*C12</f>
         <v>154</v>
       </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
@@ -1954,8 +1963,8 @@
       <c r="D13" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="87" t="s">
-        <v>47</v>
+      <c r="E13" s="58" t="s">
+        <v>46</v>
       </c>
       <c r="F13" s="38">
         <v>12</v>
@@ -1963,12 +1972,12 @@
       <c r="G13" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="59">
         <f>F13*C13</f>
         <v>600</v>
       </c>
-      <c r="I13" s="59"/>
-      <c r="J13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
@@ -1979,8 +1988,8 @@
       <c r="D14" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="87" t="s">
-        <v>48</v>
+      <c r="E14" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="F14" s="38">
         <v>23</v>
@@ -1988,12 +1997,12 @@
       <c r="G14" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="58">
+      <c r="H14" s="59">
         <f>F14*C14</f>
         <v>230</v>
       </c>
-      <c r="I14" s="59"/>
-      <c r="J14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="61"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
@@ -2004,8 +2013,8 @@
       <c r="D15" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="87" t="s">
-        <v>49</v>
+      <c r="E15" s="58" t="s">
+        <v>48</v>
       </c>
       <c r="F15" s="38">
         <v>21</v>
@@ -2013,12 +2022,12 @@
       <c r="G15" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="58">
+      <c r="H15" s="59">
         <f>F15*C15</f>
         <v>1155</v>
       </c>
-      <c r="I15" s="59"/>
-      <c r="J15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="61"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="34"/>
@@ -2029,8 +2038,8 @@
       <c r="D16" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="87" t="s">
-        <v>50</v>
+      <c r="E16" s="58" t="s">
+        <v>49</v>
       </c>
       <c r="F16" s="38">
         <v>24</v>
@@ -2038,12 +2047,12 @@
       <c r="G16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="58">
+      <c r="H16" s="59">
         <f t="shared" ref="H16:H32" si="0">F16*C16</f>
         <v>1152</v>
       </c>
-      <c r="I16" s="59"/>
-      <c r="J16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="61"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="34"/>
@@ -2054,8 +2063,8 @@
       <c r="D17" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="87" t="s">
-        <v>51</v>
+      <c r="E17" s="58" t="s">
+        <v>50</v>
       </c>
       <c r="F17" s="38">
         <v>25</v>
@@ -2063,12 +2072,12 @@
       <c r="G17" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="58">
+      <c r="H17" s="59">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I17" s="59"/>
-      <c r="J17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="61"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="34"/>
@@ -2079,8 +2088,8 @@
       <c r="D18" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="87" t="s">
-        <v>52</v>
+      <c r="E18" s="58" t="s">
+        <v>51</v>
       </c>
       <c r="F18" s="38">
         <v>13</v>
@@ -2088,12 +2097,12 @@
       <c r="G18" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="58">
+      <c r="H18" s="59">
         <f t="shared" si="0"/>
         <v>468</v>
       </c>
-      <c r="I18" s="59"/>
-      <c r="J18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="61"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="34"/>
@@ -2104,8 +2113,8 @@
       <c r="D19" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="87" t="s">
-        <v>53</v>
+      <c r="E19" s="58" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="38">
         <v>19</v>
@@ -2113,12 +2122,12 @@
       <c r="G19" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="59">
         <f t="shared" si="0"/>
         <v>1140</v>
       </c>
-      <c r="I19" s="59"/>
-      <c r="J19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="61"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="34"/>
@@ -2129,8 +2138,8 @@
       <c r="D20" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="87" t="s">
-        <v>54</v>
+      <c r="E20" s="58" t="s">
+        <v>53</v>
       </c>
       <c r="F20" s="38">
         <v>2</v>
@@ -2138,12 +2147,12 @@
       <c r="G20" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="58">
+      <c r="H20" s="59">
         <f t="shared" si="0"/>
         <v>836</v>
       </c>
-      <c r="I20" s="59"/>
-      <c r="J20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="61"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="34"/>
@@ -2154,8 +2163,8 @@
       <c r="D21" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="87" t="s">
-        <v>55</v>
+      <c r="E21" s="58" t="s">
+        <v>54</v>
       </c>
       <c r="F21" s="38">
         <v>12</v>
@@ -2163,12 +2172,12 @@
       <c r="G21" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="58">
+      <c r="H21" s="59">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="I21" s="59"/>
-      <c r="J21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="61"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="34"/>
@@ -2179,8 +2188,8 @@
       <c r="D22" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="87" t="s">
-        <v>56</v>
+      <c r="E22" s="58" t="s">
+        <v>55</v>
       </c>
       <c r="F22" s="38">
         <v>11</v>
@@ -2188,12 +2197,12 @@
       <c r="G22" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="58">
+      <c r="H22" s="59">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-      <c r="I22" s="59"/>
-      <c r="J22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="61"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="34"/>
@@ -2204,8 +2213,8 @@
       <c r="D23" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="87" t="s">
-        <v>57</v>
+      <c r="E23" s="58" t="s">
+        <v>56</v>
       </c>
       <c r="F23" s="38">
         <v>11</v>
@@ -2213,12 +2222,12 @@
       <c r="G23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="58">
+      <c r="H23" s="59">
         <f t="shared" si="0"/>
         <v>605</v>
       </c>
-      <c r="I23" s="59"/>
-      <c r="J23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="61"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="34"/>
@@ -2229,8 +2238,8 @@
       <c r="D24" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="87" t="s">
-        <v>58</v>
+      <c r="E24" s="58" t="s">
+        <v>57</v>
       </c>
       <c r="F24" s="38">
         <v>14</v>
@@ -2238,12 +2247,12 @@
       <c r="G24" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="58">
+      <c r="H24" s="59">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="I24" s="59"/>
-      <c r="J24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="61"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="34"/>
@@ -2254,8 +2263,8 @@
       <c r="D25" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="87" t="s">
-        <v>59</v>
+      <c r="E25" s="58" t="s">
+        <v>58</v>
       </c>
       <c r="F25" s="38">
         <v>12</v>
@@ -2263,12 +2272,12 @@
       <c r="G25" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="58">
+      <c r="H25" s="59">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="61"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="34"/>
@@ -2279,8 +2288,8 @@
       <c r="D26" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="87" t="s">
-        <v>60</v>
+      <c r="E26" s="58" t="s">
+        <v>59</v>
       </c>
       <c r="F26" s="38">
         <v>12</v>
@@ -2288,12 +2297,12 @@
       <c r="G26" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="58">
+      <c r="H26" s="59">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="I26" s="59"/>
-      <c r="J26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="61"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="34"/>
@@ -2304,8 +2313,8 @@
       <c r="D27" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="87" t="s">
-        <v>61</v>
+      <c r="E27" s="58" t="s">
+        <v>60</v>
       </c>
       <c r="F27" s="38">
         <v>6</v>
@@ -2313,12 +2322,12 @@
       <c r="G27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="58">
+      <c r="H27" s="59">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="I27" s="59"/>
-      <c r="J27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="61"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="34"/>
@@ -2329,8 +2338,8 @@
       <c r="D28" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="87" t="s">
-        <v>62</v>
+      <c r="E28" s="58" t="s">
+        <v>61</v>
       </c>
       <c r="F28" s="38">
         <v>23</v>
@@ -2338,12 +2347,12 @@
       <c r="G28" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="58">
+      <c r="H28" s="59">
         <f t="shared" si="0"/>
         <v>253</v>
       </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="61"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="34"/>
@@ -2354,8 +2363,8 @@
       <c r="D29" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="87" t="s">
-        <v>63</v>
+      <c r="E29" s="58" t="s">
+        <v>62</v>
       </c>
       <c r="F29" s="38">
         <v>12</v>
@@ -2363,12 +2372,12 @@
       <c r="G29" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="58">
+      <c r="H29" s="59">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="I29" s="59"/>
-      <c r="J29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="61"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="34"/>
@@ -2379,8 +2388,8 @@
       <c r="D30" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="87" t="s">
-        <v>64</v>
+      <c r="E30" s="58" t="s">
+        <v>63</v>
       </c>
       <c r="F30" s="38">
         <v>12</v>
@@ -2388,12 +2397,12 @@
       <c r="G30" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="58">
+      <c r="H30" s="59">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="I30" s="59"/>
-      <c r="J30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="61"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="34"/>
@@ -2404,8 +2413,8 @@
       <c r="D31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="87" t="s">
-        <v>65</v>
+      <c r="E31" s="58" t="s">
+        <v>64</v>
       </c>
       <c r="F31" s="38">
         <v>12</v>
@@ -2413,12 +2422,12 @@
       <c r="G31" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="58">
+      <c r="H31" s="59">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
-      <c r="I31" s="59"/>
-      <c r="J31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="61"/>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1">
       <c r="A32" s="34"/>
@@ -2429,8 +2438,8 @@
       <c r="D32" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="87" t="s">
-        <v>66</v>
+      <c r="E32" s="58" t="s">
+        <v>65</v>
       </c>
       <c r="F32" s="38">
         <v>21</v>
@@ -2438,12 +2447,12 @@
       <c r="G32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="58">
+      <c r="H32" s="59">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="I32" s="59"/>
-      <c r="J32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="61"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="34"/>
@@ -2454,8 +2463,8 @@
       <c r="D33" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="87" t="s">
-        <v>67</v>
+      <c r="E33" s="58" t="s">
+        <v>66</v>
       </c>
       <c r="F33" s="38">
         <v>12</v>
@@ -2463,12 +2472,12 @@
       <c r="G33" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H33" s="58">
+      <c r="H33" s="59">
         <f>F33*C33</f>
         <v>2040</v>
       </c>
-      <c r="I33" s="59"/>
-      <c r="J33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="61"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="34"/>
@@ -2497,12 +2506,12 @@
       <c r="E35" s="46"/>
       <c r="F35" s="47"/>
       <c r="G35" s="48"/>
-      <c r="H35" s="70">
+      <c r="H35" s="62">
         <f>SUM(H12:J34)</f>
         <v>11022</v>
       </c>
-      <c r="I35" s="71"/>
-      <c r="J35" s="72"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="64"/>
     </row>
     <row r="36" spans="1:10">
       <c r="H36" s="49"/>
@@ -2520,6 +2529,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="E4:E5"/>
@@ -2531,28 +2557,11 @@
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.21" right="0.14000000000000001" top="0.13" bottom="0.01" header="0.11999999999999998" footer="0.22"/>
@@ -2562,7 +2571,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:O43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
@@ -2575,16 +2584,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
@@ -2604,19 +2613,19 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="82" t="s">
-        <v>42</v>
+      <c r="F4" s="74" t="s">
+        <v>67</v>
       </c>
       <c r="G4" s="83"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="66"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
@@ -2624,21 +2633,21 @@
       <c r="J5" s="27"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
       <c r="E6" s="84" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="85"/>
       <c r="G6" s="85"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="66"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
       <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
@@ -2655,10 +2664,10 @@
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="78"/>
+      <c r="C10" s="79"/>
       <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
@@ -2680,8 +2689,8 @@
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="87" t="s">
-        <v>46</v>
+      <c r="B11" s="58" t="s">
+        <v>45</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="11">
@@ -2705,8 +2714,8 @@
     </row>
     <row r="12" spans="1:15" ht="17.25" customHeight="1">
       <c r="A12" s="13"/>
-      <c r="B12" s="87" t="s">
-        <v>47</v>
+      <c r="B12" s="58" t="s">
+        <v>46</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="11">
@@ -2730,8 +2739,8 @@
     </row>
     <row r="13" spans="1:15" ht="17.25" customHeight="1">
       <c r="A13" s="13"/>
-      <c r="B13" s="87" t="s">
-        <v>48</v>
+      <c r="B13" s="58" t="s">
+        <v>47</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="11">
@@ -2755,8 +2764,8 @@
     </row>
     <row r="14" spans="1:15" ht="17.25" customHeight="1">
       <c r="A14" s="13"/>
-      <c r="B14" s="87" t="s">
-        <v>49</v>
+      <c r="B14" s="58" t="s">
+        <v>48</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="11">
@@ -2780,8 +2789,8 @@
     </row>
     <row r="15" spans="1:15" ht="17.25" customHeight="1">
       <c r="A15" s="13"/>
-      <c r="B15" s="87" t="s">
-        <v>50</v>
+      <c r="B15" s="58" t="s">
+        <v>49</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="11">
@@ -2805,8 +2814,8 @@
     </row>
     <row r="16" spans="1:15" ht="17.25" customHeight="1">
       <c r="A16" s="13"/>
-      <c r="B16" s="87" t="s">
-        <v>51</v>
+      <c r="B16" s="58" t="s">
+        <v>50</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="11">
@@ -2830,8 +2839,8 @@
     </row>
     <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="A17" s="13"/>
-      <c r="B17" s="87" t="s">
-        <v>52</v>
+      <c r="B17" s="58" t="s">
+        <v>51</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="11">
@@ -2855,8 +2864,8 @@
     </row>
     <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="A18" s="13"/>
-      <c r="B18" s="87" t="s">
-        <v>53</v>
+      <c r="B18" s="58" t="s">
+        <v>52</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="11">
@@ -2880,15 +2889,15 @@
     </row>
     <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="A19" s="13"/>
-      <c r="B19" s="87" t="s">
-        <v>54</v>
+      <c r="B19" s="58" t="s">
+        <v>53</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="11">
         <v>5620</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" s="11">
         <v>418</v>
@@ -2904,8 +2913,8 @@
     </row>
     <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="A20" s="13"/>
-      <c r="B20" s="87" t="s">
-        <v>55</v>
+      <c r="B20" s="58" t="s">
+        <v>54</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="11">
@@ -2928,8 +2937,8 @@
     </row>
     <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13"/>
-      <c r="B21" s="87" t="s">
-        <v>56</v>
+      <c r="B21" s="58" t="s">
+        <v>55</v>
       </c>
       <c r="C21" s="55" t="s">
         <v>41</v>
@@ -2955,8 +2964,8 @@
     </row>
     <row r="22" spans="1:9" ht="17.25" customHeight="1">
       <c r="A22" s="13"/>
-      <c r="B22" s="87" t="s">
-        <v>57</v>
+      <c r="B22" s="58" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="11">
@@ -2980,8 +2989,8 @@
     </row>
     <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13"/>
-      <c r="B23" s="87" t="s">
-        <v>58</v>
+      <c r="B23" s="58" t="s">
+        <v>57</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="11">
@@ -3005,8 +3014,8 @@
     </row>
     <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="A24" s="13"/>
-      <c r="B24" s="87" t="s">
-        <v>59</v>
+      <c r="B24" s="58" t="s">
+        <v>58</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="11">
@@ -3030,8 +3039,8 @@
     </row>
     <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="A25" s="13"/>
-      <c r="B25" s="87" t="s">
-        <v>60</v>
+      <c r="B25" s="58" t="s">
+        <v>59</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="11">
@@ -3055,8 +3064,8 @@
     </row>
     <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="A26" s="13"/>
-      <c r="B26" s="87" t="s">
-        <v>61</v>
+      <c r="B26" s="58" t="s">
+        <v>60</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="11">
@@ -3080,8 +3089,8 @@
     </row>
     <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="13"/>
-      <c r="B27" s="87" t="s">
-        <v>62</v>
+      <c r="B27" s="58" t="s">
+        <v>61</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="11">
@@ -3105,8 +3114,8 @@
     </row>
     <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="13"/>
-      <c r="B28" s="87" t="s">
-        <v>63</v>
+      <c r="B28" s="58" t="s">
+        <v>62</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="11">
@@ -3130,8 +3139,8 @@
     </row>
     <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="13"/>
-      <c r="B29" s="87" t="s">
-        <v>64</v>
+      <c r="B29" s="58" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="11">
@@ -3155,8 +3164,8 @@
     </row>
     <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="13"/>
-      <c r="B30" s="87" t="s">
-        <v>65</v>
+      <c r="B30" s="58" t="s">
+        <v>64</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="11">
@@ -3180,8 +3189,8 @@
     </row>
     <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="13"/>
-      <c r="B31" s="87" t="s">
-        <v>66</v>
+      <c r="B31" s="58" t="s">
+        <v>65</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="11">
@@ -3205,8 +3214,8 @@
     </row>
     <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="13"/>
-      <c r="B32" s="87" t="s">
-        <v>67</v>
+      <c r="B32" s="58" t="s">
+        <v>66</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="11">
@@ -3290,7 +3299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <sheetData/>

--- a/templates/装箱单发票的格式.xlsx
+++ b/templates/装箱单发票的格式.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC15DD23-0E8E-484A-B187-E07C1CCDC819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2AECE6-A3E4-4509-9871-A91BCAE1860F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2136" yWindow="480" windowWidth="15324" windowHeight="15744" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="768" windowWidth="15324" windowHeight="15744" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOICE" sheetId="1" r:id="rId1"/>
@@ -1203,7 +1203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1390,6 +1390,27 @@
     <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1417,27 +1438,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1464,6 +1464,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1785,53 +1788,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="72" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="64"/>
       <c r="I4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
-      <c r="E5" s="65"/>
+      <c r="E5" s="72"/>
       <c r="F5" s="27" t="s">
         <v>5</v>
       </c>
@@ -1843,22 +1846,22 @@
       <c r="K5" s="53"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1">
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="73" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="74"/>
+      <c r="H6" s="64"/>
       <c r="I6" s="3"/>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1">
       <c r="A7" s="28"/>
-      <c r="E7" s="66"/>
+      <c r="E7" s="73"/>
       <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
@@ -1898,20 +1901,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="75" t="s">
+      <c r="C10" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="75"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="71" t="s">
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="69" t="s">
+      <c r="G10" s="68"/>
+      <c r="H10" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="70"/>
-      <c r="J10" s="71"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="34" t="s">
@@ -1921,10 +1924,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="68"/>
+      <c r="G11" s="75"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="J11" s="50"/>
@@ -2506,12 +2509,12 @@
       <c r="E35" s="46"/>
       <c r="F35" s="47"/>
       <c r="G35" s="48"/>
-      <c r="H35" s="62">
+      <c r="H35" s="69">
         <f>SUM(H12:J34)</f>
         <v>11022</v>
       </c>
-      <c r="I35" s="63"/>
-      <c r="J35" s="64"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
     </row>
     <row r="36" spans="1:10">
       <c r="H36" s="49"/>
@@ -2529,23 +2532,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="E4:E5"/>
@@ -2562,6 +2548,23 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.21" right="0.14000000000000001" top="0.13" bottom="0.01" header="0.11999999999999998" footer="0.22"/>
@@ -2584,16 +2587,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
@@ -2613,12 +2616,12 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="64" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="83"/>
       <c r="I4" s="82"/>
-      <c r="J4" s="74"/>
+      <c r="J4" s="64"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="B5" s="80" t="s">
@@ -2642,7 +2645,7 @@
       <c r="F6" s="85"/>
       <c r="G6" s="85"/>
       <c r="I6" s="82"/>
-      <c r="J6" s="74"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="B7" s="81"/>
@@ -2689,7 +2692,7 @@
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="87" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="10"/>
@@ -2714,7 +2717,7 @@
     </row>
     <row r="12" spans="1:15" ht="17.25" customHeight="1">
       <c r="A12" s="13"/>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="14"/>
@@ -2739,7 +2742,7 @@
     </row>
     <row r="13" spans="1:15" ht="17.25" customHeight="1">
       <c r="A13" s="13"/>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="14"/>
@@ -2764,7 +2767,7 @@
     </row>
     <row r="14" spans="1:15" ht="17.25" customHeight="1">
       <c r="A14" s="13"/>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="14"/>
@@ -2789,7 +2792,7 @@
     </row>
     <row r="15" spans="1:15" ht="17.25" customHeight="1">
       <c r="A15" s="13"/>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="14"/>
@@ -2814,7 +2817,7 @@
     </row>
     <row r="16" spans="1:15" ht="17.25" customHeight="1">
       <c r="A16" s="13"/>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="14"/>
@@ -2839,7 +2842,7 @@
     </row>
     <row r="17" spans="1:9" ht="17.25" customHeight="1">
       <c r="A17" s="13"/>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C17" s="14"/>
@@ -2864,7 +2867,7 @@
     </row>
     <row r="18" spans="1:9" ht="17.25" customHeight="1">
       <c r="A18" s="13"/>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="14"/>
@@ -2889,7 +2892,7 @@
     </row>
     <row r="19" spans="1:9" ht="17.25" customHeight="1">
       <c r="A19" s="13"/>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C19" s="14"/>
@@ -2913,7 +2916,7 @@
     </row>
     <row r="20" spans="1:9" ht="17.25" customHeight="1">
       <c r="A20" s="13"/>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="14"/>
@@ -2937,7 +2940,7 @@
     </row>
     <row r="21" spans="1:9" ht="17.25" customHeight="1">
       <c r="A21" s="13"/>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C21" s="55" t="s">
@@ -2964,7 +2967,7 @@
     </row>
     <row r="22" spans="1:9" ht="17.25" customHeight="1">
       <c r="A22" s="13"/>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="14"/>
@@ -2989,7 +2992,7 @@
     </row>
     <row r="23" spans="1:9" ht="17.25" customHeight="1">
       <c r="A23" s="13"/>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="14"/>
@@ -3014,7 +3017,7 @@
     </row>
     <row r="24" spans="1:9" ht="17.25" customHeight="1">
       <c r="A24" s="13"/>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="9" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="14"/>
@@ -3039,7 +3042,7 @@
     </row>
     <row r="25" spans="1:9" ht="17.25" customHeight="1">
       <c r="A25" s="13"/>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14"/>
@@ -3064,7 +3067,7 @@
     </row>
     <row r="26" spans="1:9" ht="17.25" customHeight="1">
       <c r="A26" s="13"/>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C26" s="14"/>
@@ -3089,7 +3092,7 @@
     </row>
     <row r="27" spans="1:9" ht="17.25" customHeight="1">
       <c r="A27" s="13"/>
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="14"/>
@@ -3114,7 +3117,7 @@
     </row>
     <row r="28" spans="1:9" ht="17.25" customHeight="1">
       <c r="A28" s="13"/>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="9" t="s">
         <v>62</v>
       </c>
       <c r="C28" s="14"/>
@@ -3139,7 +3142,7 @@
     </row>
     <row r="29" spans="1:9" ht="17.25" customHeight="1">
       <c r="A29" s="13"/>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="14"/>
@@ -3164,7 +3167,7 @@
     </row>
     <row r="30" spans="1:9" ht="17.25" customHeight="1">
       <c r="A30" s="13"/>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="9" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="14"/>
@@ -3189,7 +3192,7 @@
     </row>
     <row r="31" spans="1:9" ht="17.25" customHeight="1">
       <c r="A31" s="13"/>
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="14"/>
@@ -3214,7 +3217,7 @@
     </row>
     <row r="32" spans="1:9" ht="17.25" customHeight="1">
       <c r="A32" s="13"/>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="14"/>

--- a/templates/装箱单发票的格式.xlsx
+++ b/templates/装箱单发票的格式.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2AECE6-A3E4-4509-9871-A91BCAE1860F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34815D93-42B7-4BE0-96F8-422BBCE0A862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="768" windowWidth="15324" windowHeight="15744" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5964" yWindow="816" windowWidth="20976" windowHeight="15744" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOICE" sheetId="1" r:id="rId1"/>
@@ -1381,6 +1381,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1389,6 +1392,36 @@
     </xf>
     <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1405,39 +1438,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1464,9 +1467,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1788,53 +1788,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="66" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="64"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
-      <c r="E5" s="72"/>
+      <c r="E5" s="66"/>
       <c r="F5" s="27" t="s">
         <v>5</v>
       </c>
@@ -1846,22 +1846,22 @@
       <c r="K5" s="53"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1">
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="67" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="64"/>
+      <c r="H6" s="75"/>
       <c r="I6" s="3"/>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1">
       <c r="A7" s="28"/>
-      <c r="E7" s="73"/>
+      <c r="E7" s="67"/>
       <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
@@ -1901,20 +1901,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="67" t="s">
+      <c r="D10" s="76"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="68"/>
-      <c r="H10" s="76" t="s">
+      <c r="G10" s="78"/>
+      <c r="H10" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="77"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="34" t="s">
@@ -1924,10 +1924,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="74" t="s">
+      <c r="F11" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="75"/>
+      <c r="G11" s="69"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="J11" s="50"/>
@@ -1950,12 +1950,12 @@
       <c r="G12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="59">
+      <c r="H12" s="60">
         <f>F12*C12</f>
         <v>154</v>
       </c>
-      <c r="I12" s="60"/>
-      <c r="J12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="62"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
@@ -1975,12 +1975,12 @@
       <c r="G13" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="59">
+      <c r="H13" s="60">
         <f>F13*C13</f>
         <v>600</v>
       </c>
-      <c r="I13" s="60"/>
-      <c r="J13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="62"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
@@ -2000,12 +2000,12 @@
       <c r="G14" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="59">
+      <c r="H14" s="60">
         <f>F14*C14</f>
         <v>230</v>
       </c>
-      <c r="I14" s="60"/>
-      <c r="J14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="62"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
@@ -2025,12 +2025,12 @@
       <c r="G15" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="59">
+      <c r="H15" s="60">
         <f>F15*C15</f>
         <v>1155</v>
       </c>
-      <c r="I15" s="60"/>
-      <c r="J15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="62"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="34"/>
@@ -2050,12 +2050,12 @@
       <c r="G16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="59">
+      <c r="H16" s="60">
         <f t="shared" ref="H16:H32" si="0">F16*C16</f>
         <v>1152</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="62"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="34"/>
@@ -2075,12 +2075,12 @@
       <c r="G17" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="59">
+      <c r="H17" s="60">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="I17" s="60"/>
-      <c r="J17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="62"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="34"/>
@@ -2100,12 +2100,12 @@
       <c r="G18" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="59">
+      <c r="H18" s="60">
         <f t="shared" si="0"/>
         <v>468</v>
       </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="62"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="34"/>
@@ -2125,12 +2125,12 @@
       <c r="G19" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="59">
+      <c r="H19" s="60">
         <f t="shared" si="0"/>
         <v>1140</v>
       </c>
-      <c r="I19" s="60"/>
-      <c r="J19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="62"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="34"/>
@@ -2150,12 +2150,12 @@
       <c r="G20" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="59">
+      <c r="H20" s="60">
         <f t="shared" si="0"/>
         <v>836</v>
       </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="62"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="34"/>
@@ -2175,12 +2175,12 @@
       <c r="G21" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="59">
+      <c r="H21" s="60">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="I21" s="60"/>
-      <c r="J21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="62"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="34"/>
@@ -2200,12 +2200,12 @@
       <c r="G22" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="59">
+      <c r="H22" s="60">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="62"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="34"/>
@@ -2225,12 +2225,12 @@
       <c r="G23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="59">
+      <c r="H23" s="60">
         <f t="shared" si="0"/>
         <v>605</v>
       </c>
-      <c r="I23" s="60"/>
-      <c r="J23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="62"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="34"/>
@@ -2250,12 +2250,12 @@
       <c r="G24" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="59">
+      <c r="H24" s="60">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="62"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="34"/>
@@ -2275,12 +2275,12 @@
       <c r="G25" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="59">
+      <c r="H25" s="60">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="I25" s="60"/>
-      <c r="J25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="62"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="34"/>
@@ -2300,12 +2300,12 @@
       <c r="G26" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="59">
+      <c r="H26" s="60">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
-      <c r="I26" s="60"/>
-      <c r="J26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="62"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="34"/>
@@ -2325,12 +2325,12 @@
       <c r="G27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="59">
+      <c r="H27" s="60">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="I27" s="60"/>
-      <c r="J27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="62"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="34"/>
@@ -2350,12 +2350,12 @@
       <c r="G28" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="59">
+      <c r="H28" s="60">
         <f t="shared" si="0"/>
         <v>253</v>
       </c>
-      <c r="I28" s="60"/>
-      <c r="J28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="62"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="34"/>
@@ -2375,12 +2375,12 @@
       <c r="G29" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="59">
+      <c r="H29" s="60">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="I29" s="60"/>
-      <c r="J29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="62"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="34"/>
@@ -2400,12 +2400,12 @@
       <c r="G30" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="59">
+      <c r="H30" s="60">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="I30" s="60"/>
-      <c r="J30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="62"/>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="34"/>
@@ -2425,12 +2425,12 @@
       <c r="G31" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="59">
+      <c r="H31" s="60">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
-      <c r="I31" s="60"/>
-      <c r="J31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="62"/>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1">
       <c r="A32" s="34"/>
@@ -2450,12 +2450,12 @@
       <c r="G32" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="59">
+      <c r="H32" s="60">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="I32" s="60"/>
-      <c r="J32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="62"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="34"/>
@@ -2475,12 +2475,12 @@
       <c r="G33" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H33" s="59">
+      <c r="H33" s="60">
         <f>F33*C33</f>
         <v>2040</v>
       </c>
-      <c r="I33" s="60"/>
-      <c r="J33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="62"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="34"/>
@@ -2509,12 +2509,12 @@
       <c r="E35" s="46"/>
       <c r="F35" s="47"/>
       <c r="G35" s="48"/>
-      <c r="H35" s="69">
+      <c r="H35" s="63">
         <f>SUM(H12:J34)</f>
         <v>11022</v>
       </c>
-      <c r="I35" s="70"/>
-      <c r="J35" s="71"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="65"/>
     </row>
     <row r="36" spans="1:10">
       <c r="H36" s="49"/>
@@ -2532,6 +2532,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="E4:E5"/>
@@ -2548,23 +2565,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.21" right="0.14000000000000001" top="0.13" bottom="0.01" header="0.11999999999999998" footer="0.22"/>
@@ -2580,23 +2580,24 @@
   <cols>
     <col min="1" max="1" width="11.09765625" customWidth="1"/>
     <col min="2" max="3" width="15.8984375" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" customWidth="1"/>
     <col min="5" max="5" width="7.5" customWidth="1"/>
     <col min="6" max="6" width="8.3984375" customWidth="1"/>
-    <col min="7" max="8" width="11.19921875" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" customWidth="1"/>
+    <col min="8" max="8" width="14.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
@@ -2616,19 +2617,19 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="83"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="64"/>
+      <c r="G4" s="84"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
@@ -2636,41 +2637,41 @@
       <c r="J5" s="27"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="84" t="s">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="64"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
       <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="23.25" customHeight="1">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
     </row>
     <row r="9" spans="1:15" ht="5.25" customHeight="1"/>
     <row r="10" spans="1:15" ht="21.75" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="79"/>
+      <c r="C10" s="80"/>
       <c r="D10" s="6" t="s">
         <v>32</v>
       </c>
@@ -2692,7 +2693,7 @@
       <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="59" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="10"/>
@@ -3308,7 +3309,7 @@
   <sheetData/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/templates/装箱单发票的格式.xlsx
+++ b/templates/装箱单发票的格式.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34815D93-42B7-4BE0-96F8-422BBCE0A862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2E9427-5E2D-40F3-AE0E-1DA7C0D26A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5964" yWindow="816" windowWidth="20976" windowHeight="15744" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5196" yWindow="0" windowWidth="20976" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOICE" sheetId="1" r:id="rId1"/>
@@ -1393,6 +1393,27 @@
     <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1418,27 +1439,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1783,58 +1783,58 @@
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="8" width="6.59765625" customWidth="1"/>
     <col min="9" max="9" width="4.19921875" customWidth="1"/>
-    <col min="10" max="10" width="4.09765625" customWidth="1"/>
+    <col min="10" max="10" width="6.19921875" customWidth="1"/>
     <col min="13" max="13" width="12.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="73" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
-      <c r="E5" s="66"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="27" t="s">
         <v>5</v>
       </c>
@@ -1846,22 +1846,22 @@
       <c r="K5" s="53"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1">
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="74" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="75"/>
+      <c r="H6" s="65"/>
       <c r="I6" s="3"/>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1">
       <c r="A7" s="28"/>
-      <c r="E7" s="67"/>
+      <c r="E7" s="74"/>
       <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
@@ -1901,20 +1901,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="76"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="72" t="s">
+      <c r="D10" s="66"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="78"/>
-      <c r="H10" s="70" t="s">
+      <c r="G10" s="69"/>
+      <c r="H10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="68"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="34" t="s">
@@ -1924,10 +1924,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="69"/>
+      <c r="G11" s="76"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="J11" s="50"/>
@@ -2509,12 +2509,12 @@
       <c r="E35" s="46"/>
       <c r="F35" s="47"/>
       <c r="G35" s="48"/>
-      <c r="H35" s="63">
+      <c r="H35" s="70">
         <f>SUM(H12:J34)</f>
         <v>11022</v>
       </c>
-      <c r="I35" s="64"/>
-      <c r="J35" s="65"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
     </row>
     <row r="36" spans="1:10">
       <c r="H36" s="49"/>
@@ -2532,23 +2532,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="E4:E5"/>
@@ -2565,6 +2548,23 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.21" right="0.14000000000000001" top="0.13" bottom="0.01" header="0.11999999999999998" footer="0.22"/>
@@ -2588,16 +2588,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
@@ -2617,12 +2617,12 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="65" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="84"/>
       <c r="I4" s="83"/>
-      <c r="J4" s="75"/>
+      <c r="J4" s="65"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="B5" s="81" t="s">
@@ -2646,7 +2646,7 @@
       <c r="F6" s="86"/>
       <c r="G6" s="86"/>
       <c r="I6" s="83"/>
-      <c r="J6" s="75"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="B7" s="82"/>

--- a/templates/装箱单发票的格式.xlsx
+++ b/templates/装箱单发票的格式.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2E9427-5E2D-40F3-AE0E-1DA7C0D26A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F4A466-E75E-4B86-936F-3BEA63B2316B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5196" yWindow="0" windowWidth="20976" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1393,6 +1393,36 @@
     <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1408,37 +1438,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1781,60 +1781,61 @@
     <col min="3" max="4" width="4.8984375" customWidth="1"/>
     <col min="5" max="5" width="33.5" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="8" width="6.59765625" customWidth="1"/>
-    <col min="9" max="9" width="4.19921875" customWidth="1"/>
+    <col min="7" max="7" width="6.59765625" customWidth="1"/>
+    <col min="8" max="8" width="8.09765625" customWidth="1"/>
+    <col min="9" max="9" width="7.8984375" customWidth="1"/>
     <col min="10" max="10" width="6.19921875" customWidth="1"/>
     <col min="13" max="13" width="12.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="66" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="65"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
-      <c r="E5" s="73"/>
+      <c r="E5" s="66"/>
       <c r="F5" s="27" t="s">
         <v>5</v>
       </c>
@@ -1846,22 +1847,22 @@
       <c r="K5" s="53"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1">
-      <c r="E6" s="74" t="s">
+      <c r="E6" s="67" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="65" t="s">
+      <c r="G6" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="65"/>
+      <c r="H6" s="75"/>
       <c r="I6" s="3"/>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1">
       <c r="A7" s="28"/>
-      <c r="E7" s="74"/>
+      <c r="E7" s="67"/>
       <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
@@ -1901,20 +1902,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="68" t="s">
+      <c r="D10" s="76"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="69"/>
-      <c r="H10" s="77" t="s">
+      <c r="G10" s="78"/>
+      <c r="H10" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="78"/>
-      <c r="J10" s="68"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="34" t="s">
@@ -1924,10 +1925,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="76"/>
+      <c r="G11" s="69"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="J11" s="50"/>
@@ -2509,12 +2510,12 @@
       <c r="E35" s="46"/>
       <c r="F35" s="47"/>
       <c r="G35" s="48"/>
-      <c r="H35" s="70">
+      <c r="H35" s="63">
         <f>SUM(H12:J34)</f>
         <v>11022</v>
       </c>
-      <c r="I35" s="71"/>
-      <c r="J35" s="72"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="65"/>
     </row>
     <row r="36" spans="1:10">
       <c r="H36" s="49"/>
@@ -2532,6 +2533,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="E4:E5"/>
@@ -2548,23 +2566,6 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.21" right="0.14000000000000001" top="0.13" bottom="0.01" header="0.11999999999999998" footer="0.22"/>
@@ -2588,16 +2589,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
@@ -2617,12 +2618,12 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="F4" s="75" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="84"/>
       <c r="I4" s="83"/>
-      <c r="J4" s="65"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="B5" s="81" t="s">
@@ -2646,7 +2647,7 @@
       <c r="F6" s="86"/>
       <c r="G6" s="86"/>
       <c r="I6" s="83"/>
-      <c r="J6" s="65"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="B7" s="82"/>

--- a/templates/装箱单发票的格式.xlsx
+++ b/templates/装箱单发票的格式.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cc-picture\dd2__dd2dd.leige.site\dd2-master\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F4A466-E75E-4B86-936F-3BEA63B2316B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800F728C-5F51-4AE3-BA95-1AC7838CA43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5196" yWindow="0" windowWidth="20976" windowHeight="15744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1393,6 +1393,27 @@
     <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1418,27 +1439,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1778,7 +1778,8 @@
   <cols>
     <col min="1" max="1" width="16.3984375" customWidth="1"/>
     <col min="2" max="2" width="1.8984375" customWidth="1"/>
-    <col min="3" max="4" width="4.8984375" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="4.8984375" customWidth="1"/>
     <col min="5" max="5" width="33.5" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="6.59765625" customWidth="1"/>
@@ -1789,53 +1790,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1">
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="73" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="27" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
-      <c r="E5" s="66"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="27" t="s">
         <v>5</v>
       </c>
@@ -1847,22 +1848,22 @@
       <c r="K5" s="53"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1">
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="74" t="s">
         <v>7</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="75"/>
+      <c r="H6" s="65"/>
       <c r="I6" s="3"/>
       <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:15" ht="17.25" customHeight="1">
       <c r="A7" s="28"/>
-      <c r="E7" s="67"/>
+      <c r="E7" s="74"/>
       <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
@@ -1902,20 +1903,20 @@
         <v>14</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="76"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="72" t="s">
+      <c r="D10" s="66"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="78"/>
-      <c r="H10" s="70" t="s">
+      <c r="G10" s="69"/>
+      <c r="H10" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="68"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="34" t="s">
@@ -1925,10 +1926,10 @@
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="37"/>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="69"/>
+      <c r="G11" s="76"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
       <c r="J11" s="50"/>
@@ -2510,12 +2511,12 @@
       <c r="E35" s="46"/>
       <c r="F35" s="47"/>
       <c r="G35" s="48"/>
-      <c r="H35" s="63">
+      <c r="H35" s="70">
         <f>SUM(H12:J34)</f>
         <v>11022</v>
       </c>
-      <c r="I35" s="64"/>
-      <c r="J35" s="65"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
     </row>
     <row r="36" spans="1:10">
       <c r="H36" s="49"/>
@@ -2533,23 +2534,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="H33:J33"/>
     <mergeCell ref="H35:J35"/>
     <mergeCell ref="E4:E5"/>
@@ -2566,6 +2550,23 @@
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.21" right="0.14000000000000001" top="0.13" bottom="0.01" header="0.11999999999999998" footer="0.22"/>
@@ -2589,16 +2590,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
       <c r="I2" s="23"/>
       <c r="J2" s="23"/>
     </row>
@@ -2618,12 +2619,12 @@
       <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="65" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="84"/>
       <c r="I4" s="83"/>
-      <c r="J4" s="75"/>
+      <c r="J4" s="65"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="B5" s="81" t="s">
@@ -2647,7 +2648,7 @@
       <c r="F6" s="86"/>
       <c r="G6" s="86"/>
       <c r="I6" s="83"/>
-      <c r="J6" s="75"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="B7" s="82"/>
